--- a/Codelist Excel Files and Conversion Templates to XML/polymerType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/polymerType.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Codes for the polymer a geosynthetic reinforcement product is manufactured from. Used for the value of diggs:GeosyntheticLayerDesignType/diggs:polymerType.</t>
+          <t>Codes for the polymer a geosynthetic reinforcement product is manufactured from. Used for the value of diggs:DesignGeosyntheticLayerType/diggs:polymerType.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>//diggs:GeosyntheticLayerDesign/diggs:polymerType</t>
+          <t>//diggs:DesignGeosyntheticLayer/diggs:polymerType</t>
         </is>
       </c>
     </row>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>//diggs:GeosyntheticLayerDesign/diggs:polymerType</t>
+          <t>//diggs:DesignGeosyntheticLayer/diggs:polymerType</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>//diggs:GeosyntheticLayerDesign/diggs:polymerType</t>
+          <t>//diggs:DesignGeosyntheticLayer/diggs:polymerType</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>//diggs:GeosyntheticLayerDesign/diggs:polymerType</t>
+          <t>//diggs:DesignGeosyntheticLayer/diggs:polymerType</t>
         </is>
       </c>
     </row>
